--- a/DOSSIES_MULTIFORMATO/FMT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FMT/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE02190</t>
+          <t>2020NE02216</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1598.97</v>
+        <v>523.47</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE02216</t>
+          <t>2020NE02190</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>523.47</v>
+        <v>1598.97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,19 +681,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022NE0001462</t>
+          <t>2022NE0001461</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1532</v>
+        <v>4794.48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE NOVEMBRO/22</t>
+          <t>reforço</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022NE0001461</t>
+          <t>2022NE0001462</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4794.48</v>
+        <v>1532</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>reforço</t>
+          <t>PARA ATENDER O MÊS DE NOVEMBRO/22</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2019NE02195</t>
+          <t>2019NE02205</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>844.75</v>
+        <v>400</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2019NE02205</t>
+          <t>2019NE02195</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>400</v>
+        <v>844.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -942,12 +942,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2017NE00732</t>
+          <t>2017NE00730</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6444.32</v>
+        <v>4578.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1002,12 +1002,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2017NE00730</t>
+          <t>2017NE00732</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4578.6</v>
+        <v>6444.32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025NE0000565</t>
+          <t>2025NE0000566</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18918.81</v>
+        <v>2717.66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025NE0000566</t>
+          <t>2025NE0000565</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2717.66</v>
+        <v>18918.81</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1115,14 +1115,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022NE0001856</t>
+          <t>2022NE0001886</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>121.26</v>
+        <v>1097.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1141,14 +1141,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 242, SALDO DE EMPENHO</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022NE0001872</t>
+          <t>2022NE0001875</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1362.08</v>
+        <v>1608.84</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1167,14 +1167,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 1462, SALDO DE EMPENHO</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2022NE0001875</t>
+          <t>2022NE0001872</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1608.84</v>
+        <v>1362.08</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1193,14 +1193,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO PARCIAL DA NE 1462, SALDO DE EMPENHO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2022NE0001886</t>
+          <t>2022NE0001856</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1097.4</v>
+        <v>121.26</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>ANULAÇÃO PARCIAL DA NE 242, SALDO DE EMPENHO</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018NE02067</t>
+          <t>2018NE02044</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9328.780000000001</v>
+        <v>352.87</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1331,14 +1331,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO, PARA AJUSTE ORÇAMENTO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2018NE02045</t>
+          <t>2018NE02015</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.18</v>
+        <v>282.98</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2018NE02015</t>
+          <t>2018NE02045</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>282.98</v>
+        <v>8.18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE02044</t>
+          <t>2018NE02067</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>352.87</v>
+        <v>9328.780000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1435,28 +1435,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>ANULAÇÃO DO SALDO, PARA AJUSTE ORÇAMENTO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025NE0001861</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2025NE0001860</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>28/11/2025</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9666.48</v>
+        <v>9810.82</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1465,19 +1461,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>REFERENTE AO 3ºT.A. DO CONTRATO Nº 009/14,REFERENTE A EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA EM GERAL - SERVIÇOS FIREWALL,REFERENTE AS NOTAS FISCAIS N°25298,25840 E 26145,COMPETÊ</t>
+          <t>REFERENTE AO TERMO DE CONVÊNIO Nº 001/2018-CESSÃO SERVIDOR - FABRICIO ROGÉRIO CYRINO BARBOSA,PACTUADO NA FORMA DA LEI ENTRE A PRODAM, REFERENTE AO MÊS DE DEZEMBRO/18.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025NE0001859</t>
+          <t>2025NE0001862</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1486,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>536.9299999999999</v>
+        <v>13706.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1495,7 +1491,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAGAMENTO,REFERENTE AO 2º T.A. DO </t>
+          <t>REFERENTE A EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO Á INTERNET,CONTRATO Nº 002/2013,REFERENTE AS FATURAS Nº20584 E 21034 COMPETÊNCIAS NOVEMBRO E DEZEMBRO/2016. FATURA Nº 26144,COMPETÊN</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1528,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025NE0001862</t>
+          <t>2025NE0001859</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1546,7 +1542,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13706.9</v>
+        <v>536.9299999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1555,24 +1551,28 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>REFERENTE A EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO Á INTERNET,CONTRATO Nº 002/2013,REFERENTE AS FATURAS Nº20584 E 21034 COMPETÊNCIAS NOVEMBRO E DEZEMBRO/2016. FATURA Nº 26144,COMPETÊN</t>
+          <t xml:space="preserve">REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAGAMENTO,REFERENTE AO 2º T.A. DO </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025NE0001860</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>2025NE0001861</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>28/11/2025</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9810.82</v>
+        <v>9666.48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1581,24 +1581,28 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>REFERENTE AO TERMO DE CONVÊNIO Nº 001/2018-CESSÃO SERVIDOR - FABRICIO ROGÉRIO CYRINO BARBOSA,PACTUADO NA FORMA DA LEI ENTRE A PRODAM, REFERENTE AO MÊS DE DEZEMBRO/18.</t>
+          <t>REFERENTE AO 3ºT.A. DO CONTRATO Nº 009/14,REFERENTE A EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE INFORMÁTICA EM GERAL - SERVIÇOS FIREWALL,REFERENTE AS NOTAS FISCAIS N°25298,25840 E 26145,COMPETÊ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022NE0001340</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>2022NE0001343</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>28/09/2022</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1328.08</v>
+        <v>9588.959999999999</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1607,7 +1611,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
@@ -1644,21 +1648,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022NE0001343</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2022NE0001340</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>28/09/2022</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9588.959999999999</v>
+        <v>1328.08</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
@@ -1734,10 +1734,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2023NE0000851</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2023NE00851</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9/2022</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>28/06/2023</t>
@@ -1753,24 +1757,28 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>REFERENTE AO CONTRATO 009/2022, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE SISTEMA PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023NE0000849</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>2023NE0000850</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>28/06/2023</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>18918.81</v>
+        <v>4976.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1779,7 +1787,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>PARA ATENDER CT 006/19</t>
         </is>
       </c>
     </row>
@@ -1816,21 +1824,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023NE0000850</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2023NE0000849</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>28/06/2023</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4976.2</v>
+        <v>18918.81</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1839,21 +1843,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT 006/19</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2023NE00851</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>9/2022</t>
-        </is>
-      </c>
+          <t>2023NE0000851</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>28/06/2023</t>
@@ -1869,19 +1869,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>REFERENTE AO CONTRATO 009/2022, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE SISTEMA PRODAM-RH.</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2022NE0000523</t>
+          <t>2022NE0000524</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1000</v>
+        <v>1328.08</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1899,19 +1899,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VALOR REFERENTE AO INICIO DO NOVO ADITIVO DE CONTRATO</t>
+          <t>REF AO MES DE ABRIL/22 DO CONTRATO DE LOCAÇÃO DE EQUIPAMENTOS.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2022NE0000524</t>
+          <t>2022NE0000523</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1328.08</v>
+        <v>1000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1929,24 +1929,28 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>REF AO MES DE ABRIL/22 DO CONTRATO DE LOCAÇÃO DE EQUIPAMENTOS.</t>
+          <t>VALOR REFERENTE AO INICIO DO NOVO ADITIVO DE CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020NE00198</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>2020NE00199</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>28/02/2020</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>578.6900000000001</v>
+        <v>4066.91</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1988,21 +1992,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020NE00199</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2020NE00198</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>28/02/2020</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4066.91</v>
+        <v>578.6900000000001</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2074,17 +2074,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2022NE0000510</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>2022NE0000502</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>27/04/2022</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1328.08</v>
+        <v>4794.48</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2093,19 +2097,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>CONTRATO PARA ATENDER A FMTHVD</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2022NE0000503</t>
+          <t>2022NE0000512</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2114,7 +2118,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1328.08</v>
+        <v>15704.02</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2156,12 +2160,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2022NE0000512</t>
+          <t>2022NE0000503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2170,7 +2174,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15704.02</v>
+        <v>1328.08</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2186,21 +2190,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2022NE0000502</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2022NE0000510</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>27/04/2022</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4794.48</v>
+        <v>1328.08</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2209,14 +2209,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CONTRATO PARA ATENDER A FMTHVD</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2021NE0000118</t>
+          <t>2021NE0000128</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3984.24</v>
+        <v>8133.82</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2021NE0000128</t>
+          <t>2021NE0000118</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8133.82</v>
+        <v>3984.24</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2023NE0001456</t>
+          <t>2023NE0001455</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1532</v>
+        <v>4976.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Contratação de serviços de um sistema de folha de pagamento informatizado denominado Plantão mensal/anual.</t>
+          <t>Contratação de empresa para Prestação do Serviço de Firewall para a FMT-HVD. TC: 006/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2023NE0001455</t>
+          <t>2023NE0001456</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4976.2</v>
+        <v>1532</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2467,24 +2467,28 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação do Serviço de Firewall para a FMT-HVD. TC: 006/2019 AD: 04.</t>
+          <t>Contratação de serviços de um sistema de folha de pagamento informatizado denominado Plantão mensal/anual.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2022NE0000950</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>2022NE0000948</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>26/07/2022</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18227.95</v>
+        <v>4794.48</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2493,19 +2497,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>REF AO MES DE JUNHO/2022</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0000952</t>
+          <t>2022NE0000951</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2514,7 +2518,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>18227.95</v>
+        <v>1328.08</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2560,12 +2564,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2022NE0000951</t>
+          <t>2022NE0000952</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2574,7 +2578,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1328.08</v>
+        <v>18227.95</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2590,21 +2594,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2022NE0000948</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2022NE0000950</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>26/07/2022</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4794.48</v>
+        <v>18227.95</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>REF AO MES DE JUNHO/2022</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2023NE0000515</t>
+          <t>2023NE00515</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2673,14 +2673,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CT- 009/19</t>
+          <t xml:space="preserve">Referente ao Contrato 009/2019 - 4º TA contratação de empresa especializada em Prestação de Serviços de Tecnologia de Informação, compreendendo a Hospedagem de Infraestrutura virtualizada para compor </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2023NE00515</t>
+          <t>2023NE0000515</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente ao Contrato 009/2019 - 4º TA contratação de empresa especializada em Prestação de Serviços de Tecnologia de Informação, compreendendo a Hospedagem de Infraestrutura virtualizada para compor </t>
+          <t>PARA ATENDER O CT- 009/19</t>
         </is>
       </c>
     </row>
@@ -2740,12 +2740,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024NE0000301</t>
+          <t>2024NE0000302</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4976.2</v>
+        <v>18918.81</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 40677, MÊS SETEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
+          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2024NE0000302</t>
+          <t>2024NE0000301</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>18918.81</v>
+        <v>4976.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
+          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 40677, MÊS SETEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2022NE0000943</t>
+          <t>2022NE0000941</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>84.13</v>
+        <v>281.7</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANUL PARCIAL DA NE 649</t>
+          <t>ANULAÇÃO PARCIAL DA NE 524</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2022NE0000941</t>
+          <t>2022NE0000943</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>281.7</v>
+        <v>84.13</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2927,19 +2927,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 524</t>
+          <t>ANUL PARCIAL DA NE 649</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026NE0000113</t>
+          <t>2026NE0000096</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3186.3</v>
+        <v>17831.59</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2957,19 +2957,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026NE0000100</t>
+          <t>2026NE0000097</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4976.2</v>
+        <v>17831.59</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2987,19 +2987,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026NE0000105</t>
+          <t>2026NE0000106</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5325.53</v>
+        <v>2855.17</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3017,19 +3017,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026NE0000114</t>
+          <t>2026NE0000095</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>953.12</v>
+        <v>17831.59</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3047,19 +3047,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026NE0000117</t>
+          <t>2026NE0000108</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>378.68</v>
+        <v>2855.17</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3077,19 +3077,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026NE0000098</t>
+          <t>2026NE0000110</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>17831.59</v>
+        <v>2855.17</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3107,19 +3107,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026NE0000109</t>
+          <t>2026NE0000102</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2855.17</v>
+        <v>5325.53</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3137,14 +3137,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026NE0000107</t>
+          <t>2026NE0000111</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3174,12 +3174,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026NE0000104</t>
+          <t>2026NE0000099</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5325.53</v>
+        <v>17831.59</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3197,14 +3197,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026NE0000101</t>
+          <t>2026NE0000103</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026NE0000103</t>
+          <t>2026NE0000101</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026NE0000099</t>
+          <t>2026NE0000104</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17831.59</v>
+        <v>5325.53</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3287,14 +3287,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026NE0000111</t>
+          <t>2026NE0000107</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3324,12 +3324,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026NE0000102</t>
+          <t>2026NE0000109</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5325.53</v>
+        <v>2855.17</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3347,19 +3347,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026NE0000110</t>
+          <t>2026NE0000098</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2855.17</v>
+        <v>17831.59</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3377,19 +3377,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026NE0000108</t>
+          <t>2026NE0000117</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2855.17</v>
+        <v>378.68</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3407,19 +3407,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026NE0000095</t>
+          <t>2026NE0000114</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>17831.59</v>
+        <v>953.12</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3437,19 +3437,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026NE0000106</t>
+          <t>2026NE0000105</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2855.17</v>
+        <v>5325.53</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3467,19 +3467,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026NE0000097</t>
+          <t>2026NE0000100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>17831.59</v>
+        <v>4976.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3497,19 +3497,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026NE0000096</t>
+          <t>2026NE0000113</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7/2025</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>17831.59</v>
+        <v>3186.3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2023NE0001797</t>
+          <t>2023NE0001812</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1532</v>
+        <v>181.72</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2023NE0001808</t>
+          <t>2023NE0001823</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>647.65</v>
+        <v>2882.28</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2023NE0001823</t>
+          <t>2023NE0001808</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2882.28</v>
+        <v>647.65</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2023NE0001812</t>
+          <t>2023NE0001797</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>181.72</v>
+        <v>1532</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO PARCIAL DA NE</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2023NE0000213</t>
+          <t>2023NE0000212</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>181.72</v>
+        <v>4794.48</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3751,14 +3751,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>PARA ATENDER CT- 4ºT.A.- 006/19</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2023NE0000212</t>
+          <t>2023NE0000213</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4794.48</v>
+        <v>181.72</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3781,14 +3781,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT- 4ºT.A.- 006/19</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2023NE0000834</t>
+          <t>2023NE0000832</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>659.42</v>
+        <v>4976.2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3814,17 +3814,21 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2023NE0000833</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>2023NE0000822</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>9/2022</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>23/06/2023</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>18918.81</v>
+        <v>659.42</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3833,19 +3837,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>PARA ATENDER CR 009/2022</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2023NE0000821</t>
+          <t>2023NE0000820</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3854,7 +3858,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4976.2</v>
+        <v>18918.81</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3863,19 +3867,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT 006/19</t>
+          <t>PARA ATENDER CT 009/19</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2023NE0000820</t>
+          <t>2023NE0000821</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3884,7 +3888,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>18918.81</v>
+        <v>4976.2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3893,28 +3897,24 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT 009/19</t>
+          <t>PARA ATENDER CT 006/19</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2023NE0000822</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>9/2022</t>
-        </is>
-      </c>
+          <t>2023NE0000833</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
           <t>23/06/2023</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>659.42</v>
+        <v>18918.81</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3923,14 +3923,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PARA ATENDER CR 009/2022</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2023NE0000832</t>
+          <t>2023NE0000834</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4976.2</v>
+        <v>659.42</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2023NE0000384</t>
+          <t>2023NE00384</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3979,14 +3979,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>REFERENTE AO CONTRATO Nº 009/2022, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAGAMENT</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2023NE00384</t>
+          <t>2023NE0000384</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4009,19 +4009,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>REFERENTE AO CONTRATO Nº 009/2022, CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAGAMENT</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2023NE0000205</t>
+          <t>2023NE0000204</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1532</v>
+        <v>18227.95</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4046,12 +4046,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2023NE0000204</t>
+          <t>2023NE0000205</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>18227.95</v>
+        <v>1532</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4102,17 +4102,21 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE02099</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>2015NE02108</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>22/12/2015</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>13875.62</v>
+        <v>3222.16</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4121,19 +4125,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 596, SALDO DE CONTRATO.</t>
+          <t>SERV</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2015NE02107</t>
+          <t>2015NE02105</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4142,7 +4146,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10917</v>
+        <v>717.77</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4151,19 +4155,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ACESSO A INTERNET</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2015NE02105</t>
+          <t>2015NE02107</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4172,7 +4176,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>717.77</v>
+        <v>10917</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4181,28 +4185,24 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>ACESSO A INTERNET</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2015NE02108</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2015NE02099</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>22/12/2015</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3222.16</v>
+        <v>13875.62</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4211,19 +4211,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SERV</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 596, SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2024NE0001224</t>
+          <t>2024NE0001223</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10870.64</v>
+        <v>4976.2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4241,19 +4241,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2024NE0001223</t>
+          <t>2024NE0001224</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4976.2</v>
+        <v>10870.64</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4271,19 +4271,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023NE0001165</t>
+          <t>2023NE0001166</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1532</v>
+        <v>18918.81</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4301,14 +4301,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>reforço</t>
+          <t>PARA ATENDER CT N° 009/2019</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2023NE0001167</t>
+          <t>2023NE0001169</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>181.72</v>
+        <v>4976.2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2023NE0001169</t>
+          <t>2023NE0001167</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4976.2</v>
+        <v>181.72</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4379,19 +4379,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2023NE0001166</t>
+          <t>2023NE0001165</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>18918.81</v>
+        <v>1532</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4409,19 +4409,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT N° 009/2019</t>
+          <t>reforço</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025NE0000691</t>
+          <t>2025NE0000689</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4794.48</v>
+        <v>2717.66</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4476,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025NE0000689</t>
+          <t>2025NE0000691</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2717.66</v>
+        <v>4794.48</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4499,14 +4499,14 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024NE0000620</t>
+          <t>2024NE0000624</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 04.</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2024NE0000624</t>
+          <t>2024NE0000620</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2021NE0001666</t>
+          <t>2021NE0001667</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2252.43</v>
+        <v>802.0700000000001</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2021NE0001671</t>
+          <t>2021NE0001670</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>793.14</v>
+        <v>803.48</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4678,21 +4678,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2021NE0001672</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2021NE0001668</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>21/10/2021</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3984.24</v>
+        <v>1589.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4701,28 +4697,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMTHVD</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021NE0001680</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2021NE0001669</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>21/10/2021</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4066.91</v>
+        <v>804.89</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4731,24 +4723,28 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMTHVD</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2021NE0001669</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>2021NE0001680</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
           <t>21/10/2021</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>804.89</v>
+        <v>4066.91</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4757,24 +4753,28 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>PARA ATENDER A FMTHVD</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2021NE0001668</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>2021NE0001672</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
           <t>21/10/2021</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1589.1</v>
+        <v>3984.24</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4783,14 +4783,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>PARA ATENDER A FMTHVD</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2021NE0001670</t>
+          <t>2021NE0001671</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>803.48</v>
+        <v>793.14</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2021NE0001667</t>
+          <t>2021NE0001666</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>802.0700000000001</v>
+        <v>2252.43</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5022,12 +5022,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2016NE01813</t>
+          <t>2016NE01805</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1831.44</v>
+        <v>3222.16</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5045,19 +5045,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2016NE01814</t>
+          <t>2016NE01806</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3222.16</v>
+        <v>915.72</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5075,19 +5075,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2016NE01806</t>
+          <t>2016NE01814</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>915.72</v>
+        <v>3222.16</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5105,19 +5105,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2016NE01805</t>
+          <t>2016NE01813</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3222.16</v>
+        <v>1831.44</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>.</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2018NE01399</t>
+          <t>2018NE01400</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5466.68</v>
+        <v>3222.16</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5195,19 +5195,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE MARÇO/18.</t>
+          <t>PARA ATENDER O MÊS DE ABRIL/18.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2018NE01400</t>
+          <t>2018NE01399</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3222.16</v>
+        <v>5466.68</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5225,19 +5225,19 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE ABRIL/18.</t>
+          <t>PARA ATENDER O MÊS DE MARÇO/18.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2022NE0000701</t>
+          <t>2022NE0000686</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>981.42</v>
+        <v>1328.08</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5255,19 +5255,19 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>CONTRATO PARA ATENDER A FMTHVD</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2022NE0000686</t>
+          <t>2022NE0000701</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1328.08</v>
+        <v>981.42</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5285,28 +5285,24 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CONTRATO PARA ATENDER A FMTHVD</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021NE0000691</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>9/2019</t>
-        </is>
-      </c>
+          <t>2021NE0000672</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>20/05/2021</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>31408.04</v>
+        <v>2170.04</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5315,7 +5311,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>PÁRA ATENDER OS MESES DE MAIO E JUNHO/21</t>
+          <t>PARA ATENDER O MÊS DE MAIO/21</t>
         </is>
       </c>
     </row>
@@ -5348,17 +5344,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021NE0000672</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>2021NE0000691</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9/2019</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr">
         <is>
           <t>20/05/2021</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2170.04</v>
+        <v>31408.04</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5367,17 +5367,21 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE MAIO/21</t>
+          <t>PÁRA ATENDER OS MESES DE MAIO E JUNHO/21</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2023NE0000004</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>2023NE0000003</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>9/2019</t>
+        </is>
+      </c>
       <c r="C167" t="inlineStr">
         <is>
           <t>20/01/2023</t>
@@ -5393,21 +5397,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>PARA ATENDER O CONTRATO Nº 009/2019 - 3ºT.A. MÊS DE JANEIRO/23</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2023NE0000003</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>9/2019</t>
-        </is>
-      </c>
+          <t>2023NE0000004</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>20/01/2023</t>
@@ -5423,19 +5423,19 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CONTRATO Nº 009/2019 - 3ºT.A. MÊS DE JANEIRO/23</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021NE0000023</t>
+          <t>2021NE0000024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3984.24</v>
+        <v>47112.06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5460,12 +5460,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021NE0000024</t>
+          <t>2021NE0000023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>47112.06</v>
+        <v>3984.24</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5520,12 +5520,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2017NE01471</t>
+          <t>2017NE01472</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5458.5</v>
+        <v>3222.16</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5543,19 +5543,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PARA ATENDER MÊS DE JULHO/17 - CONTRATO Nº 002/13</t>
+          <t>PARA ATENDER O MÊS DE AGOSTO/17 - CONTRATO Nº 009/14</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2017NE01472</t>
+          <t>2017NE01471</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3222.16</v>
+        <v>5458.5</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE AGOSTO/17 - CONTRATO Nº 009/14</t>
+          <t>PARA ATENDER MÊS DE JULHO/17 - CONTRATO Nº 002/13</t>
         </is>
       </c>
     </row>
@@ -5610,17 +5610,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2022NE0000662</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>2022NE0000663</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
           <t>19/05/2022</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4066.91</v>
+        <v>4794.48</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5629,7 +5633,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>CONTRATO PARA ATENDER A FMTHVD</t>
         </is>
       </c>
     </row>
@@ -5666,21 +5670,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2022NE0000663</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2022NE0000662</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>19/05/2022</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4794.48</v>
+        <v>4066.91</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CONTRATO PARA ATENDER A FMTHVD</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2020NE02163</t>
+          <t>2020NE02162</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>19.04</v>
+        <v>1612.6</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2020NE02162</t>
+          <t>2020NE02163</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1612.6</v>
+        <v>19.04</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2018NE01427</t>
+          <t>2018NE01423</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>8.18</v>
+        <v>1211.25</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5831,14 +5831,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE SETEMBRO/18.</t>
+          <t>PARA ATENDER O MÊS DE SETEMBRO/18 - CONTRATO Nº 022/17</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2018NE01423</t>
+          <t>2018NE01427</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1211.25</v>
+        <v>8.18</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE SETEMBRO/18 - CONTRATO Nº 022/17</t>
+          <t>PARA ATENDER O MÊS DE SETEMBRO/18.</t>
         </is>
       </c>
     </row>
@@ -5898,12 +5898,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2020NE00618</t>
+          <t>2020NE00619</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1328.08</v>
+        <v>4066.91</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>PARA ATENDER MÊS DE MAIO/20</t>
+          <t>PARA ATENDER O MÊS DE MAIO/20</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,11 @@
           <t>2020NE00620</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>9/2019</t>
+        </is>
+      </c>
       <c r="C186" t="inlineStr">
         <is>
           <t>18/05/2020</t>
@@ -5957,11 +5961,7 @@
           <t>2020NE00620</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>9/2019</t>
-        </is>
-      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
           <t>18/05/2020</t>
@@ -5984,12 +5984,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2020NE00619</t>
+          <t>2020NE00618</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4066.91</v>
+        <v>1328.08</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6007,19 +6007,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE MAIO/20</t>
+          <t>PARA ATENDER MÊS DE MAIO/20</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2022NE0001530</t>
+          <t>2022NE0001529</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>18227.95</v>
+        <v>4794.48</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6074,12 +6074,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2022NE0001529</t>
+          <t>2022NE0001530</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4794.48</v>
+        <v>18227.95</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025NE0001458</t>
+          <t>2025NE0001456</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6127,19 +6127,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 42955, MÊS DEZEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
+          <t>OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 41306, MÊS OUTUBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO D</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025NE0001457</t>
+          <t>2025NE0001459</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4976.2</v>
+        <v>18918.81</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6157,14 +6157,14 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 44951, MÊS NOVEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
+          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025NE0001454</t>
+          <t>2025NE0001460</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6187,14 +6187,14 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
+          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025NE0001455</t>
+          <t>2025NE0001461</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6217,14 +6217,14 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
+          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025NE0001461</t>
+          <t>2025NE0001455</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6247,14 +6247,14 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025NE0001460</t>
+          <t>2025NE0001454</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6277,19 +6277,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025NE0001459</t>
+          <t>2025NE0001457</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>18918.81</v>
+        <v>4976.2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6307,14 +6307,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>OBJETO: CONTRATAÇÃO DE SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO, HOSPEDAGEM EM INFRAESTRUTURA VIRTUALIZADA PARA COMPORTAR O SISTEMA INTEGRADO DE GESTÃO HOSPITALAR – IDOCTOR.REFERENTE AS NOTAS FISCAIS Nº 4</t>
+          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 44951, MÊS NOVEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025NE0001456</t>
+          <t>2025NE0001458</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6337,19 +6337,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 41306, MÊS OUTUBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO D</t>
+          <t xml:space="preserve">OBJETO: REFERENTE A CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DO SERVIÇO DE FIREWALL PARA A FMT-HVD.REFERENTE A NOTA FISCAL Nº 42955, MÊS DEZEMBRO/2023.CONTRATO Nº 0006/2019 – ADITIVO Nº 4º - PRORROGAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021NE0001187</t>
+          <t>2021NE0001188</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4066.91</v>
+        <v>1328.08</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>REF AO MES DE AGOSTO 21</t>
+          <t>REF AO MES DE AGOSTO/21</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021NE0001188</t>
+          <t>2021NE0001187</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1328.08</v>
+        <v>4066.91</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6427,14 +6427,14 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>REF AO MES DE AGOSTO/21</t>
+          <t>REF AO MES DE AGOSTO 21</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2020NE00940</t>
+          <t>2020NE00939</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>31408.04</v>
+        <v>542.51</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6457,19 +6457,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JULHO E AGOSTO/20</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2020NE00949</t>
+          <t>2020NE00953</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>8133.82</v>
+        <v>2656.16</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6524,12 +6524,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2020NE00953</t>
+          <t>2020NE00949</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2656.16</v>
+        <v>8133.82</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2020NE00939</t>
+          <t>2020NE00940</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>542.51</v>
+        <v>31408.04</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6577,14 +6577,14 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>PARA ATENDER OS MESES DE JULHO E AGOSTO/20</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025NE00834</t>
+          <t>2025NE0000834</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Referente ao Contrato 003/2024 - Fornecimento de Licença de uso de Sistema de Informação, compreendendo a disponibilização do Gestor de Conteúdo Web - GERWEB.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025NE00835</t>
+          <t>2025NE0000835</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6637,14 +6637,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Referente ao 1º TA ao Contrato 003/2024 - Serviço de Fornecimento de Licença de uso de Sistema de informação, compreendendo a disponibilização do Gestor de Conteúdo Web - GERWEB.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025NE0000836</t>
+          <t>2025NE00836</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6667,14 +6667,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
+          <t>Referente ao Contrato 007/2025 - Serviço de Tecnologia da Informação Hospedagem em Infraestrutura Virtualizada.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025NE00836</t>
+          <t>2025NE0000836</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Referente ao Contrato 007/2025 - Serviço de Tecnologia da Informação Hospedagem em Infraestrutura Virtualizada.</t>
+          <t>Contratação de Serviço de Tecnologia da Informação, compreendendo a Hospedagem em infraestrutura virtualizada</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025NE0000835</t>
+          <t>2025NE00835</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Referente ao 1º TA ao Contrato 003/2024 - Serviço de Fornecimento de Licença de uso de Sistema de informação, compreendendo a disponibilização do Gestor de Conteúdo Web - GERWEB.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025NE0000834</t>
+          <t>2025NE00834</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Referente ao Contrato 003/2024 - Fornecimento de Licença de uso de Sistema de Informação, compreendendo a disponibilização do Gestor de Conteúdo Web - GERWEB.</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2023NE0000676</t>
+          <t>2023NE00673</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>36274.18</v>
+        <v>181.72</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 009/2019 AD: 03.</t>
+          <t>Referente ao Contrato 009/2019 - 3º TA Contratação de empresa especializada em Prestação de Serviços de TI, compreendendo a Hospedagem em estrutura virtualizada para compor o Sistema I-DOCTOR.</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2023NE00673</t>
+          <t>2023NE0000676</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>181.72</v>
+        <v>36274.18</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6955,19 +6955,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Referente ao Contrato 009/2019 - 3º TA Contratação de empresa especializada em Prestação de Serviços de TI, compreendendo a Hospedagem em estrutura virtualizada para compor o Sistema I-DOCTOR.</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 009/2019 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2015NE00411</t>
+          <t>2015NE00408</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>9126.02</v>
+        <v>5250</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6985,19 +6985,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Cobertura 2015 -Mês de Março</t>
+          <t>Cobertura financeira 2015 - Mês de Março</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2015NE00408</t>
+          <t>2015NE00411</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7006,7 +7006,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5250</v>
+        <v>9126.02</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7015,19 +7015,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015 - Mês de Março</t>
+          <t>Cobertura 2015 -Mês de Março</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2020NE00345</t>
+          <t>2020NE00347</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1328.08</v>
+        <v>16246.53</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7082,12 +7082,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2020NE00347</t>
+          <t>2020NE00345</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>16246.53</v>
+        <v>1328.08</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7142,10 +7142,14 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2020NE01217</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr"/>
+          <t>2020NE01232</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C227" t="inlineStr">
         <is>
           <t>15/09/2020</t>
@@ -7161,21 +7165,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SOLICITADO NA VIGÊNCIA INDEVIDA.</t>
+          <t>PARA ATENDER A FMT-HVD.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2020NE01232</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2020NE01217</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
           <t>15/09/2020</t>
@@ -7191,19 +7191,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMT-HVD.</t>
+          <t>SOLICITADO NA VIGÊNCIA INDEVIDA.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2023NE0000668</t>
+          <t>2023NE00669</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1532</v>
+        <v>4976.2</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7221,19 +7221,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT 009/22 - MÊS DE ABRIL/23</t>
+          <t>Referente ao 4º TA da contratação de empresa especializada na prestação de serviços de informática em geral, referente ao Contrato nº 006/2019.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2023NE0000669</t>
+          <t>2023NE00668</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>4976.2</v>
+        <v>1532</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT 006/19 - MÊS DE ABRIL/23</t>
+          <t>Referente ao Contrato nº 009/2022 contratação de empresa especializada em Prestação de Serviços de Desenvolvimento de Software aplicativo para controle de Pessoal e Processamento de Folha de Pagamento</t>
         </is>
       </c>
     </row>
@@ -7284,12 +7284,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2023NE00668</t>
+          <t>2023NE0000669</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1532</v>
+        <v>4976.2</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7307,19 +7307,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Referente ao Contrato nº 009/2022 contratação de empresa especializada em Prestação de Serviços de Desenvolvimento de Software aplicativo para controle de Pessoal e Processamento de Folha de Pagamento</t>
+          <t>PARA ATENDER CT 006/19 - MÊS DE ABRIL/23</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2023NE00669</t>
+          <t>2023NE0000668</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4976.2</v>
+        <v>1532</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Referente ao 4º TA da contratação de empresa especializada na prestação de serviços de informática em geral, referente ao Contrato nº 006/2019.</t>
+          <t>PARA ATENDER CT 009/22 - MÊS DE ABRIL/23</t>
         </is>
       </c>
     </row>
@@ -7370,12 +7370,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2019NE00085</t>
+          <t>2019NE00084</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1648.11</v>
+        <v>325.95</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7393,19 +7393,19 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PARA ATENDER A COMPLEMENTAÇÃO DE JANEIRO A MARÇO/19.</t>
+          <t>COMPLEMENTAÇÃO DOS MESES DE JANEIRO A M,ARÇO/19</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2019NE00084</t>
+          <t>2019NE00085</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>325.95</v>
+        <v>1648.11</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7423,19 +7423,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>COMPLEMENTAÇÃO DOS MESES DE JANEIRO A M,ARÇO/19</t>
+          <t>PARA ATENDER A COMPLEMENTAÇÃO DE JANEIRO A MARÇO/19.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2020NE01459</t>
+          <t>2020NE01455</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>15704.02</v>
+        <v>4066.91</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7453,19 +7453,19 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE NOVEMBRO/20</t>
+          <t>PARA ATENDER O MÊS DE DEZEMBRO/20</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2020NE01458</t>
+          <t>2020NE01452</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>15704.02</v>
+        <v>4066.91</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7483,19 +7483,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE OUTUBRO/20</t>
+          <t>PARA ATENDER O MÊS DE NOVEMBRO/20</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2020NE01452</t>
+          <t>2020NE01458</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>4066.91</v>
+        <v>15704.02</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7513,19 +7513,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE NOVEMBRO/20</t>
+          <t>PARA ATENDER O MÊS DE OUTUBRO/20</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2020NE01455</t>
+          <t>2020NE01459</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>4066.91</v>
+        <v>15704.02</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE DEZEMBRO/20</t>
+          <t>PARA ATENDER O MÊS DE NOVEMBRO/20</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2024NE0002095</t>
+          <t>2024NE0002103</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE MAIO/2024.PARECER JURDÍDICO Nº 252/2024-ASJUR/FMT-HVD. TAC Nº 003/2024.</t>
+          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE JULHO/2024.PARECER JURDÍDICO Nº 246/2024-ASJUR/FMT-HVD.TAC Nº 005/2024.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2024NE0002093</t>
+          <t>2024NE0002094</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7629,19 +7629,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE MARÇO/2024. PARECER JURDÍDICO Nº 256/2024-ASJUR/FMT-HVD. TAC Nº 001/2024.</t>
+          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE ABRIL/2024. PARECER JURDÍDICO Nº 258/2024-ASJUR/FMT-HVD. TAC Nº 002/2024.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2024NE0002102</t>
+          <t>2024NE0002092</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>4976.2</v>
+        <v>56756.43</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7659,19 +7659,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE JUNHO/2024.PARECER JURDÍDICO Nº 254/2024-ASJUR/FMT-HVD.TAC Nº 004/2024.</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2024NE0002092</t>
+          <t>2024NE0002102</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>56756.43</v>
+        <v>4976.2</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 05.</t>
+          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE JUNHO/2024.PARECER JURDÍDICO Nº 254/2024-ASJUR/FMT-HVD.TAC Nº 004/2024.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2024NE0002094</t>
+          <t>2024NE0002093</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7719,14 +7719,14 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE ABRIL/2024. PARECER JURDÍDICO Nº 258/2024-ASJUR/FMT-HVD. TAC Nº 002/2024.</t>
+          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE MARÇO/2024. PARECER JURDÍDICO Nº 256/2024-ASJUR/FMT-HVD. TAC Nº 001/2024.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2024NE0002103</t>
+          <t>2024NE0002095</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE JULHO/2024.PARECER JURDÍDICO Nº 246/2024-ASJUR/FMT-HVD.TAC Nº 005/2024.</t>
+          <t>REGRENTE AO SERVIÇO DE INFORMÁTICA NA GESTÃO DE SEGURANÇA E ATIVOS DE REDE PACOTE ESSENCIAL.REFERENTE AO MÊS DE MAIO/2024.PARECER JURDÍDICO Nº 252/2024-ASJUR/FMT-HVD. TAC Nº 003/2024.</t>
         </is>
       </c>
     </row>
@@ -7816,12 +7816,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2021NE0000482</t>
+          <t>2021NE0000484</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>15704.02</v>
+        <v>1328.08</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7876,12 +7876,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2021NE0000484</t>
+          <t>2021NE0000482</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1328.08</v>
+        <v>15704.02</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025NE0001921</t>
+          <t>2025NE0001922</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025NE0001925</t>
+          <t>2025NE0001923</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>171.6</v>
+        <v>945.9400000000001</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO PARCIAL.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025NE0001924</t>
+          <t>2025NE0001919</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>945.9400000000001</v>
+        <v>171.6</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025NE0001919</t>
+          <t>2025NE0001924</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>171.6</v>
+        <v>945.9400000000001</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>ANULAÇÃO PARCIAL.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025NE0001923</t>
+          <t>2025NE0001925</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>945.9400000000001</v>
+        <v>171.6</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8055,14 +8055,14 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025NE0001922</t>
+          <t>2025NE0001921</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -8088,10 +8088,14 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2020NE01205</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
+          <t>2020NE01207</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
           <t>11/09/2020</t>
@@ -8107,21 +8111,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>PARA ATENDER FMT-HVD</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2020NE01207</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2020NE01205</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
           <t>11/09/2020</t>
@@ -8137,21 +8137,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>PARA ATENDER FMT-HVD</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2022NE0001088</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2022NE0001090</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
           <t>11/08/2022</t>
@@ -8167,17 +8163,21 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AGOSTO CONTRATO DE EQUIP DE INFORMATICA</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2022NE0001090</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr"/>
+          <t>2022NE0001088</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr">
         <is>
           <t>11/08/2022</t>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>AGOSTO CONTRATO DE EQUIP DE INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2022NE0001061</t>
+          <t>2022NE0001062</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>4794.48</v>
+        <v>36455.9</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8253,19 +8253,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CONTRATO DE SERV DE INFORMATICA</t>
+          <t>REFERENTE AOS MESES DE JULHO E AGOSTO</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2022NE0001062</t>
+          <t>2022NE0001061</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>36455.9</v>
+        <v>4794.48</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>REFERENTE AOS MESES DE JULHO E AGOSTO</t>
+          <t>CONTRATO DE SERV DE INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2020NE01733</t>
+          <t>2020NE01732</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2134.38</v>
+        <v>805.36</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2020NE01730</t>
+          <t>2020NE01731</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1835.4</v>
+        <v>807.24</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2020NE01731</t>
+          <t>2020NE01730</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>807.24</v>
+        <v>1835.4</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2020NE01732</t>
+          <t>2020NE01733</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>805.36</v>
+        <v>2134.38</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8450,12 +8450,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2015NE00908</t>
+          <t>2015NE00897</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3222.16</v>
+        <v>5250</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>COBERTURA MAIO 2015</t>
+          <t>reforço do contrato</t>
         </is>
       </c>
     </row>
@@ -8510,12 +8510,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2015NE00897</t>
+          <t>2015NE00908</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>5250</v>
+        <v>3222.16</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8533,19 +8533,19 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>reforço do contrato</t>
+          <t>COBERTURA MAIO 2015</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2021NE0001811</t>
+          <t>2021NE0001812</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>4066.91</v>
+        <v>15704.02</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8570,12 +8570,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2021NE0001812</t>
+          <t>2021NE0001811</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>15704.02</v>
+        <v>4066.91</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8600,10 +8600,14 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2020NE01180</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
+          <t>2020NE01184</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr">
         <is>
           <t>08/09/2020</t>
@@ -8619,19 +8623,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>PARA ATENDER OS MESES NOV E DEZ/20</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2020NE01181</t>
+          <t>2020NE01179</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8640,7 +8644,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1328.08</v>
+        <v>4066.91</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8649,19 +8653,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS NOV/20</t>
+          <t>PARA ATENDER O M~ES OUTUBRO/20</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2020NE01179</t>
+          <t>2020NE01181</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8670,7 +8674,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>4066.91</v>
+        <v>1328.08</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8679,21 +8683,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>PARA ATENDER O M~ES OUTUBRO/20</t>
+          <t>PARA ATENDER O MÊS NOV/20</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2020NE01184</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2020NE01180</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
           <t>08/09/2020</t>
@@ -8709,19 +8709,19 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES NOV E DEZ/20</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2021NE0000944</t>
+          <t>2021NE0000945</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>15704.02</v>
+        <v>1328.08</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>REF A JULHO/21</t>
+          <t>REF AO MES DE JULHO/21</t>
         </is>
       </c>
     </row>
@@ -8776,12 +8776,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2021NE0000945</t>
+          <t>2021NE0000944</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1328.08</v>
+        <v>15704.02</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8799,19 +8799,19 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>REF AO MES DE JULHO/21</t>
+          <t>REF A JULHO/21</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2021NE0000735</t>
+          <t>2021NE0000734</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8133.82</v>
+        <v>2656.16</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8829,19 +8829,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>PARA ATENDER FMTHVD , REF AOS MESES DE MAIO E JUNHO/21</t>
+          <t>PARA ATENDER FMTHVD , REF. AOS MESES DE MAIO E JUNHO/21</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2021NE0000734</t>
+          <t>2021NE0000735</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>2656.16</v>
+        <v>8133.82</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8859,19 +8859,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PARA ATENDER FMTHVD , REF. AOS MESES DE MAIO E JUNHO/21</t>
+          <t>PARA ATENDER FMTHVD , REF AOS MESES DE MAIO E JUNHO/21</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2017NE00795</t>
+          <t>2017NE00796</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>10917</v>
+        <v>1831.44</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8926,12 +8926,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2017NE00796</t>
+          <t>2017NE00795</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1831.44</v>
+        <v>10917</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8956,12 +8956,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2015NE00597</t>
+          <t>2015NE00595</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>9126.02</v>
+        <v>3222.16</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Cobertura financeira do mes de abril 2015</t>
+          <t>Cobertura financeira do mês de abril/15</t>
         </is>
       </c>
     </row>
@@ -9016,12 +9016,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2015NE00595</t>
+          <t>2015NE00597</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>3222.16</v>
+        <v>9126.02</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9039,19 +9039,19 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Cobertura financeira do mês de abril/15</t>
+          <t>Cobertura financeira do mes de abril 2015</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025NE0000249</t>
+          <t>2025NE0000251</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>2717.66</v>
+        <v>4794.48</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
         </is>
       </c>
     </row>
@@ -9106,12 +9106,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025NE0000251</t>
+          <t>2025NE0000249</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>4794.48</v>
+        <v>2717.66</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026NE0000171</t>
+          <t>2026NE0000173</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>4794.48</v>
+        <v>2717.66</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9309,19 +9309,19 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026NE0000173</t>
+          <t>2026NE0000171</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2717.66</v>
+        <v>4794.48</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
@@ -9402,12 +9402,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026NE0000012</t>
+          <t>2026NE0000010</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>2719.01</v>
+        <v>4794.48</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9425,19 +9425,19 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026NE0000010</t>
+          <t>2026NE0000012</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4794.48</v>
+        <v>2719.01</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9455,19 +9455,19 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados. TC: 0002/2024 AD: 01.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2015NE00071</t>
+          <t>2015NE00053</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>7325.76</v>
+        <v>6260.28</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9485,19 +9485,19 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>SOFTWARE</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2015NE00092</t>
+          <t>2015NE00091</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>18252.04</v>
+        <v>10500</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -9515,14 +9515,14 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - meses: janeiro a fevereiro</t>
+          <t>Cobertura financeira 2015 - meses: janeiro e fevereiro</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2015NE00070</t>
+          <t>2015NE00052</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº52, EM VIRTUDE DE TER SIDO EMPENHADO NA REFERÊNCIA INDEVIDA.</t>
+          <t>CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2015NE00074</t>
+          <t>2015NE00073</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9575,14 +9575,14 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº71, EM VIRTUDE DE TER SIDO EMPENHADO NA REFERENCIA INDEVIDA.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2015NE00073</t>
+          <t>2015NE00074</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9605,14 +9605,14 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº71, EM VIRTUDE DE TER SIDO EMPENHADO NA REFERENCIA INDEVIDA.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2015NE00052</t>
+          <t>2015NE00070</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9635,19 +9635,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CONTRATO</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº52, EM VIRTUDE DE TER SIDO EMPENHADO NA REFERÊNCIA INDEVIDA.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2015NE00091</t>
+          <t>2015NE00092</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>10500</v>
+        <v>18252.04</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9665,19 +9665,19 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015 - meses: janeiro e fevereiro</t>
+          <t>Cobertura Financeira 2015 - meses: janeiro a fevereiro</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2015NE00053</t>
+          <t>2015NE00071</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>6260.28</v>
+        <v>7325.76</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>SOFTWARE</t>
         </is>
       </c>
     </row>
@@ -9728,21 +9728,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2017NE01983</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2/2013</t>
-        </is>
-      </c>
+          <t>2017NE01859</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
           <t>04/12/2017</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>5640.45</v>
+        <v>1675</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9751,24 +9747,28 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>PARA ATENDER AGOSTO E SETEMBRO/17</t>
+          <t>.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2017NE01859</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr"/>
+          <t>2017NE01983</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2/2013</t>
+        </is>
+      </c>
       <c r="C317" t="inlineStr">
         <is>
           <t>04/12/2017</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1675</v>
+        <v>5640.45</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>PARA ATENDER AGOSTO E SETEMBRO/17</t>
         </is>
       </c>
     </row>
@@ -9870,12 +9870,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2021NE0000207</t>
+          <t>2021NE0000208</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>47112.06</v>
+        <v>12200.73</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/21</t>
+          <t>PARA TANEDER OS MESES DE JANEIRO A MARÇO/21</t>
         </is>
       </c>
     </row>
@@ -9930,12 +9930,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2021NE0000208</t>
+          <t>2021NE0000207</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>12200.73</v>
+        <v>47112.06</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -9953,24 +9953,28 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>PARA TANEDER OS MESES DE JANEIRO A MARÇO/21</t>
+          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/21</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2025NE0001874</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr"/>
+          <t>2025NE0001905</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>3/2024</t>
+        </is>
+      </c>
       <c r="C324" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>2459.97</v>
+        <v>960.55</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -9979,24 +9983,28 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2025NE0001899</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr"/>
+          <t>2025NE0001904</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>3/2024</t>
+        </is>
+      </c>
       <c r="C325" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>542.9</v>
+        <v>1894.62</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10005,14 +10013,14 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2025NE0001873</t>
+          <t>2025NE0001889</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -10022,7 +10030,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1288.88</v>
+        <v>1894.62</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -10038,7 +10046,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2025NE0001875</t>
+          <t>2025NE0001876</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -10048,7 +10056,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>322.22</v>
+        <v>293.35</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10090,7 +10098,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2025NE0001876</t>
+          <t>2025NE0001875</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -10100,7 +10108,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>293.35</v>
+        <v>322.22</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10116,7 +10124,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2025NE0001889</t>
+          <t>2025NE0001873</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -10126,7 +10134,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1894.62</v>
+        <v>1288.88</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10142,21 +10150,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2025NE0001904</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>3/2024</t>
-        </is>
-      </c>
+          <t>2025NE0001899</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1894.62</v>
+        <v>542.9</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10165,28 +10169,24 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2025NE0001905</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>3/2024</t>
-        </is>
-      </c>
+          <t>2025NE0001874</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
       <c r="C332" t="inlineStr">
         <is>
           <t>03/12/2025</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>960.55</v>
+        <v>2459.97</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10195,14 +10195,14 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web TC: 0003/2024 AD: 01.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2020NE01636</t>
+          <t>2020NE01630</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>581.01</v>
+        <v>4066.91</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2020NE01615</t>
+          <t>2020NE01627</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>6016.05</v>
+        <v>4066.91</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2020NE01640</t>
+          <t>2020NE01626</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>539.25</v>
+        <v>4066.91</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2020NE01614</t>
+          <t>2020NE01618</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>6016.05</v>
+        <v>4066.91</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2020NE01633</t>
+          <t>2020NE01669</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1922.38</v>
+        <v>15704.02</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2020NE01641</t>
+          <t>2020NE01616</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>539.25</v>
+        <v>6016.05</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2020NE01644</t>
+          <t>2020NE01617</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>925.28</v>
+        <v>4066.91</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2020NE01613</t>
+          <t>2020NE01667</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>6016.05</v>
+        <v>15704.02</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2020NE01658</t>
+          <t>2020NE01666</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>6510.15</v>
+        <v>15704.02</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>PARA ATENDER REC.DIVIDAS</t>
+          <t>PARA ATENDER RD</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2020NE01661</t>
+          <t>2020NE01665</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>6016.05</v>
+        <v>13781.64</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2020NE01665</t>
+          <t>2020NE01661</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>13781.64</v>
+        <v>6016.05</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2020NE01666</t>
+          <t>2020NE01658</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>15704.02</v>
+        <v>6510.15</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10507,14 +10507,14 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>PARA ATENDER RD</t>
+          <t>PARA ATENDER REC.DIVIDAS</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2020NE01667</t>
+          <t>2020NE01613</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>15704.02</v>
+        <v>6016.05</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2020NE01617</t>
+          <t>2020NE01644</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>4066.91</v>
+        <v>925.28</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2020NE01616</t>
+          <t>2020NE01641</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>6016.05</v>
+        <v>539.25</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2020NE01669</t>
+          <t>2020NE01633</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>15704.02</v>
+        <v>1922.38</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2020NE01618</t>
+          <t>2020NE01614</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>4066.91</v>
+        <v>6016.05</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2020NE01626</t>
+          <t>2020NE01640</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>4066.91</v>
+        <v>539.25</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2020NE01627</t>
+          <t>2020NE01615</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>4066.91</v>
+        <v>6016.05</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2020NE01630</t>
+          <t>2020NE01636</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -10706,7 +10706,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>4066.91</v>
+        <v>581.01</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2021NE0001357</t>
+          <t>2021NE0001359</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10778,7 +10778,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2021NE0001359</t>
+          <t>2021NE0001357</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -10804,12 +10804,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2020NE01152</t>
+          <t>2020NE01153</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2656.16</v>
+        <v>31408.04</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE AGOSTO E SETEMBRO/20</t>
+          <t>PARA ATENDER OS MESES DE SETEMBRO E OUTUBRO/20</t>
         </is>
       </c>
     </row>
@@ -10864,12 +10864,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2020NE01153</t>
+          <t>2020NE01152</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>31408.04</v>
+        <v>2656.16</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE SETEMBRO E OUTUBRO/20</t>
+          <t>PARA ATENDER OS MESES DE AGOSTO E SETEMBRO/20</t>
         </is>
       </c>
     </row>
@@ -10950,12 +10950,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2025NE0000772</t>
+          <t>2025NE0000771</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>4794.48</v>
+        <v>2717.66</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -10973,19 +10973,19 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2025NE0000771</t>
+          <t>2025NE0000772</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2717.66</v>
+        <v>4794.48</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11003,19 +11003,19 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2019NE00827</t>
+          <t>2019NE00819</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1328.08</v>
+        <v>4066.91</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11070,12 +11070,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2019NE00819</t>
+          <t>2019NE00827</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>4066.91</v>
+        <v>1328.08</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11100,12 +11100,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2022NE0000020</t>
+          <t>2022NE0000031</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>47112.06</v>
+        <v>8133.82</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>REF AOS MESES DE JAN A MARÇO /2022</t>
+          <t>PARA ATENDER A FMT</t>
         </is>
       </c>
     </row>
@@ -11160,12 +11160,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2022NE0000031</t>
+          <t>2022NE0000020</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>8133.82</v>
+        <v>47112.06</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11183,19 +11183,19 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMT</t>
+          <t>REF AOS MESES DE JAN A MARÇO /2022</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2025NE0001869</t>
+          <t>2025NE0001867</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>5867.1</v>
+        <v>25777.28</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>REFERENTE AO 2ºT.A. DO CONTRATO Nº 022/2017,CONTRATÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAG</t>
+          <t>REFERENTE AO CONTRATO Nº 009/14,REFERENTE A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS EM GERAL - SERVIÇOS FIREWALL. REFERENTE AS NOTAS FISCAIS ECOMPETÊNCIAS: N.F 1839 - 05/2018 N.F 2307 - 06/2018</t>
         </is>
       </c>
     </row>
@@ -11250,12 +11250,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2025NE0001867</t>
+          <t>2025NE0001869</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>25777.28</v>
+        <v>5867.1</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>REFERENTE AO CONTRATO Nº 009/14,REFERENTE A EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS EM GERAL - SERVIÇOS FIREWALL. REFERENTE AS NOTAS FISCAIS ECOMPETÊNCIAS: N.F 1839 - 05/2018 N.F 2307 - 06/2018</t>
+          <t>REFERENTE AO 2ºT.A. DO CONTRATO Nº 022/2017,CONTRATÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DESENVOLVIMENTO DE SOFTWARE APLICATIVO PARA CONTROLE DE PESSOAL E PROCESSAMENTO DE FOLHA DE PAG</t>
         </is>
       </c>
     </row>
@@ -11306,12 +11306,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2021NE0001327</t>
+          <t>2021NE0001328</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>15704.02</v>
+        <v>4066.91</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11366,12 +11366,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2021NE0001328</t>
+          <t>2021NE0001327</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>4066.91</v>
+        <v>15704.02</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -11396,14 +11396,10 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2019NE01519</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2019NE01416</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr">
         <is>
           <t>02/09/2019</t>
@@ -11419,17 +11415,21 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE SETEMBRO/19</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2019NE01416</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr"/>
+          <t>2019NE01519</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C377" t="inlineStr">
         <is>
           <t>02/09/2019</t>
@@ -11445,28 +11445,24 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>PARA ATENDER O MÊS DE SETEMBRO/19</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024NE0000953</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>3/2024</t>
-        </is>
-      </c>
+          <t>2024NE0000952</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr">
         <is>
           <t>02/07/2024</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2717.66</v>
+        <v>5435.32</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11475,24 +11471,28 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024NE0000952</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr"/>
+          <t>2024NE0000953</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>3/2024</t>
+        </is>
+      </c>
       <c r="C379" t="inlineStr">
         <is>
           <t>02/07/2024</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>5435.32</v>
+        <v>2717.66</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
@@ -11568,12 +11568,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2019NE00594</t>
+          <t>2019NE00661</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>4066.91</v>
+        <v>844.75</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11591,19 +11591,19 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>PARA ATENDER O MÊS DE MAIO/19</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2019NE00592</t>
+          <t>2019NE00500</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>6016.05</v>
+        <v>4066.91</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>reforço</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2019NE00500</t>
+          <t>2019NE00592</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>4066.91</v>
+        <v>6016.05</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11681,19 +11681,19 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>reforço</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2019NE00661</t>
+          <t>2019NE00594</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>844.75</v>
+        <v>4066.91</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11711,24 +11711,28 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE MAIO/19</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2016NE00735</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr"/>
+          <t>2016NE00738</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2/2013</t>
+        </is>
+      </c>
       <c r="C387" t="inlineStr">
         <is>
           <t>02/05/2016</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>10032.09</v>
+        <v>5458.5</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -11737,19 +11741,19 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 177, EM VIRTUDE DA SUSPENSÃO DO CONTRATO Nº 003/2013,CONFORME OFICIO Nº 0533/2016-GDF/FMT-HVD.</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2016NE00737</t>
+          <t>2016NE00736</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11758,7 +11762,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>3222.16</v>
+        <v>915.72</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11774,12 +11778,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2016NE00736</t>
+          <t>2016NE00737</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11788,7 +11792,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>915.72</v>
+        <v>3222.16</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11804,21 +11808,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2016NE00738</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>2/2013</t>
-        </is>
-      </c>
+          <t>2016NE00735</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
           <t>02/05/2016</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>5458.5</v>
+        <v>10032.09</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 177, EM VIRTUDE DA SUSPENSÃO DO CONTRATO Nº 003/2013,CONFORME OFICIO Nº 0533/2016-GDF/FMT-HVD.</t>
         </is>
       </c>
     </row>
@@ -11894,17 +11894,21 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2018NE00338</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr"/>
+          <t>2018NE00368</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C393" t="inlineStr">
         <is>
           <t>02/03/2018</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>3222.16</v>
+        <v>1219.44</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -11913,19 +11917,19 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>PARA ATENDER DT-022/17</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2018NE00369</t>
+          <t>2018NE00370</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11934,7 +11938,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3222.16</v>
+        <v>5466.68</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -11943,7 +11947,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>para atender o CT. 009/14</t>
+          <t>PARA ATENDER CT - 004/18</t>
         </is>
       </c>
     </row>
@@ -11976,12 +11980,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2018NE00370</t>
+          <t>2018NE00369</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11990,7 +11994,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>5466.68</v>
+        <v>3222.16</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -11999,28 +12003,24 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT - 004/18</t>
+          <t>para atender o CT. 009/14</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2018NE00368</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2018NE00338</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
         <is>
           <t>02/03/2018</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1219.44</v>
+        <v>3222.16</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>PARA ATENDER DT-022/17</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
@@ -12066,12 +12066,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2025NE0000010</t>
+          <t>2025NE0000073</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12080,7 +12080,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>4794.48</v>
+        <v>2717.66</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
+          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2025NE0000073</t>
+          <t>2025NE0000010</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>3/2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>2717.66</v>
+        <v>4794.48</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12149,19 +12149,19 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Contratação para serviço de fornecimento de licença de uso de sistema de informação, compreendendo a disponibilização do gestor de conteúdo web</t>
+          <t>Contratação de serviço de Gestão de Segurança da Informação, através do fornecimento de Firewall e serviços correlatados.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024NE0000101</t>
+          <t>2024NE0000058</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>37837.62</v>
+        <v>9588.959999999999</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12179,19 +12179,19 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 04.</t>
+          <t>Contratação de empresa para Prestação do Serviço de Firewall para a FMT-HVD. TC: 0006/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024NE0000058</t>
+          <t>2024NE0000101</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12200,7 +12200,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>9588.959999999999</v>
+        <v>37837.62</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12209,19 +12209,19 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Contratação de empresa para Prestação do Serviço de Firewall para a FMT-HVD. TC: 0006/2019 AD: 04.</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR TC: 0009/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2023NE0000051</t>
+          <t>2023NE0000001</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>9/2019</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>18227.95</v>
+        <v>1532</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR</t>
+          <t>PARA ATENDER O CONTRATO Nº 009/2022 - MÊS DE JANEIRO/23</t>
         </is>
       </c>
     </row>
@@ -12276,12 +12276,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2023NE0000001</t>
+          <t>2023NE0000051</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2019</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1532</v>
+        <v>18227.95</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12299,28 +12299,24 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CONTRATO Nº 009/2022 - MÊS DE JANEIRO/23</t>
+          <t>Contratação de serviços de tecnologia da Informação, hospedagem em infraestrutura virtualizada para comportar Sistema Integrado de Gestão Hospitalar - IDOCTOR</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2020NE00061</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>9/2019</t>
-        </is>
-      </c>
+          <t>2020NE00013</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>48739.59</v>
+        <v>12200.73</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12329,14 +12325,14 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/2020.</t>
+          <t>ANULAÇÃO TOTAL</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2020NE00016</t>
+          <t>2020NE00003</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12350,7 +12346,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>8133.82</v>
+        <v>12200.73</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12359,7 +12355,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JANEIRO E FEVEREIRO/20.</t>
+          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/20.</t>
         </is>
       </c>
     </row>
@@ -12396,7 +12392,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
+          <t>2020NE00016</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12410,7 +12406,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>12200.73</v>
+        <v>8133.82</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12419,24 +12415,28 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/20.</t>
+          <t>PARA ATENDER OS MESES DE JANEIRO E FEVEREIRO/20.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2020NE00013</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr"/>
+          <t>2020NE00061</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>9/2019</t>
+        </is>
+      </c>
       <c r="C411" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>12200.73</v>
+        <v>48739.59</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12445,19 +12445,19 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL</t>
+          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/2020.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2019NE00073</t>
+          <t>2019NE00074</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3658.32</v>
+        <v>16400.04</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>PARA OS MESES DE JANEIRO A MARÇO/19.</t>
+          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/19.</t>
         </is>
       </c>
     </row>
@@ -12512,12 +12512,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2019NE00074</t>
+          <t>2019NE00073</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12526,7 +12526,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>16400.04</v>
+        <v>3658.32</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -12535,19 +12535,19 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>PARA ATENDER OS MESES DE JANEIRO A MARÇO/19.</t>
+          <t>PARA OS MESES DE JANEIRO A MARÇO/19.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2018NE00004</t>
+          <t>2018NE00145</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>3222.16</v>
+        <v>1219.44</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -12565,19 +12565,19 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE SETEMBRO/17 - EXERC.ANT.</t>
+          <t>PARA ATENDER O M~ES DE JANEIRO/18 - CONT.022/17 - PRODAM</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2018NE00103</t>
+          <t>2018NE00146</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>2789.9</v>
+        <v>3222.16</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE NOV/17.</t>
+          <t>PARA ATENDER O M~ES DE JANEIRO/18 - CONT.009/14</t>
         </is>
       </c>
     </row>
@@ -12632,12 +12632,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2018NE00146</t>
+          <t>2018NE00103</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -12646,7 +12646,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>3222.16</v>
+        <v>2789.9</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -12655,19 +12655,19 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>PARA ATENDER O M~ES DE JANEIRO/18 - CONT.009/14</t>
+          <t>PARA ATENDER O MÊS DE NOV/17.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2018NE00145</t>
+          <t>2018NE00004</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12676,7 +12676,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1219.44</v>
+        <v>3222.16</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -12685,19 +12685,19 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>PARA ATENDER O M~ES DE JANEIRO/18 - CONT.022/17 - PRODAM</t>
+          <t>PARA ATENDER O MÊS DE SETEMBRO/17 - EXERC.ANT.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2017NE00161</t>
+          <t>2017NE00159</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -12706,7 +12706,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>5458.5</v>
+        <v>3222.16</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -12752,12 +12752,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2017NE00159</t>
+          <t>2017NE00161</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3222.16</v>
+        <v>5458.5</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -12782,12 +12782,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2014NE00059</t>
+          <t>2014NE00046</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12796,7 +12796,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>104416.68</v>
+        <v>6784.4</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2013 - Internet 3Mbps</t>
+          <t>Contrato No. 12/2012 - CFPP,(Colaboradores em regime de plantão)</t>
         </is>
       </c>
     </row>
@@ -12842,12 +12842,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2014NE00046</t>
+          <t>2014NE00059</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -12856,7 +12856,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>6784.4</v>
+        <v>104416.68</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Contrato No. 12/2012 - CFPP,(Colaboradores em regime de plantão)</t>
+          <t>Contrato No. 2/2013 - Internet 3Mbps</t>
         </is>
       </c>
     </row>
@@ -12898,12 +12898,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2016NE01748</t>
+          <t>2016NE01757</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>2522.66</v>
+        <v>5458.5</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -12921,19 +12921,19 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2016NE01749</t>
+          <t>2016NE01750</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>6444.32</v>
+        <v>10917</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -12958,12 +12958,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2016NE01750</t>
+          <t>2016NE01749</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>10917</v>
+        <v>6444.32</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -12988,12 +12988,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2016NE01757</t>
+          <t>2016NE01748</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>5458.5</v>
+        <v>2522.66</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -13011,14 +13011,14 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2015NE01973</t>
+          <t>2015NE01965</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>3222.16</v>
+        <v>6444.32</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>LOCAÇÃO</t>
+          <t>serviços INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13078,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2015NE01965</t>
+          <t>2015NE01973</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13092,7 +13092,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>6444.32</v>
+        <v>3222.16</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -13101,21 +13101,17 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>serviços INFORMATICA</t>
+          <t>LOCAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2018NE01577</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>22/2017</t>
-        </is>
-      </c>
+          <t>2018NE01541</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
           <t>01/10/2018</t>
@@ -13131,17 +13127,21 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE OUTUBRO/18.</t>
+          <t>ANULAÇÃO PARCIAL</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2018NE01541</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr"/>
+          <t>2018NE01577</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>22/2017</t>
+        </is>
+      </c>
       <c r="C435" t="inlineStr">
         <is>
           <t>01/10/2018</t>
@@ -13157,14 +13157,14 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL</t>
+          <t>PARA ATENDER O MÊS DE OUTUBRO/18.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2015NE01580</t>
+          <t>2015NE01581</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1882.38</v>
+        <v>94.03</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 74,SALDO DE CONTRATO.</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 1252,SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2015NE01581</t>
+          <t>2015NE01580</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>94.03</v>
+        <v>1882.38</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 1252,SALDO DE CONTRATO.</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 74,SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
@@ -13314,12 +13314,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2015NE01316</t>
+          <t>2015NE01314</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>3222.16</v>
+        <v>763.17</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -13337,19 +13337,19 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE SOFTWARE</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 91, SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2015NE01252</t>
+          <t>2015NE01315</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>915.72</v>
+        <v>297.75</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -13367,19 +13367,19 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>COBERTURA SET.2015</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 408, SALDO DE CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2015NE01254</t>
+          <t>2015NE01317</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>6444.32</v>
+        <v>5458.5</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -13397,19 +13397,19 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>COBERTURA JUNHO E JULHO/2015 - VALOR MENSAL R$ 3.222,16</t>
+          <t>COBERTURA AGOSTO/2015</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2015NE01253</t>
+          <t>2015NE01255</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>5250</v>
+        <v>18252.04</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -13427,19 +13427,19 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>COBERTURA JUNHO.2015</t>
+          <t>COBERTURA JUNHO E JULHO 2015 - VALOR MENSAL R$ 9.126,02</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2015NE01255</t>
+          <t>2015NE01253</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>18252.04</v>
+        <v>5250</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -13457,19 +13457,19 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>COBERTURA JUNHO E JULHO 2015 - VALOR MENSAL R$ 9.126,02</t>
+          <t>COBERTURA JUNHO.2015</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2015NE01317</t>
+          <t>2015NE01254</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>5458.5</v>
+        <v>6444.32</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -13487,19 +13487,19 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>COBERTURA AGOSTO/2015</t>
+          <t>COBERTURA JUNHO E JULHO/2015 - VALOR MENSAL R$ 3.222,16</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2015NE01315</t>
+          <t>2015NE01252</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>297.75</v>
+        <v>915.72</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -13517,19 +13517,19 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 408, SALDO DE CONTRATO.</t>
+          <t>COBERTURA SET.2015</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2015NE01314</t>
+          <t>2015NE01316</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -13538,7 +13538,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>763.17</v>
+        <v>3222.16</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 91, SALDO DE CONTRATO.</t>
+          <t>LOCAÇÃO DE SOFTWARE</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2015NE00871</t>
+          <t>2015NE00872</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -13689,14 +13689,14 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>EXERC.</t>
+          <t>EXERC.ANT.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2015NE00872</t>
+          <t>2015NE00871</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -13715,21 +13715,17 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>EXERC.ANT.</t>
+          <t>EXERC.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2019NE00339</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2019NE00315</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr">
         <is>
           <t>01/04/2019</t>
@@ -13745,19 +13741,19 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMT-HVD. PRODAM PROCESSAMENTO</t>
+          <t>ANULAÇÃO TOTAL DA NE 268, EM VIRTUDE DE NÃO TER INFORMADO A DESCRIÇÃO CORRETA.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2019NE00347</t>
+          <t>2019NE00349</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13766,7 +13762,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>6016.05</v>
+        <v>1328.08</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -13775,19 +13771,19 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMT-HVD. PRODAM CONTRATO 004/2018</t>
+          <t>PARA ATENDER A FMT-HVD. PRODAM CONTRATO Nº 022/2017</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2019NE00349</t>
+          <t>2019NE00347</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13796,7 +13792,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1328.08</v>
+        <v>6016.05</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -13805,17 +13801,21 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>PARA ATENDER A FMT-HVD. PRODAM CONTRATO Nº 022/2017</t>
+          <t>PARA ATENDER A FMT-HVD. PRODAM CONTRATO 004/2018</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2019NE00315</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr"/>
+          <t>2019NE00339</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C458" t="inlineStr">
         <is>
           <t>01/04/2019</t>
@@ -13831,19 +13831,19 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE 268, EM VIRTUDE DE NÃO TER INFORMADO A DESCRIÇÃO CORRETA.</t>
+          <t>PARA ATENDER A FMT-HVD. PRODAM PROCESSAMENTO</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2016NE00549</t>
+          <t>2016NE00551</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1831.44</v>
+        <v>10917</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -13861,19 +13861,19 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>REFORÇO</t>
+          <t>PRODAM</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2016NE00551</t>
+          <t>2016NE00549</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>10917</v>
+        <v>1831.44</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>PRODAM</t>
+          <t>REFORÇO</t>
         </is>
       </c>
     </row>
@@ -13958,14 +13958,10 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2019NE00268</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2019NE00264</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr">
         <is>
           <t>01/03/2019</t>
@@ -13981,7 +13977,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>A CONTRATADA obriga-se a prestar para a CONTRATANTE a Prestação do Serviço de firewall, compreendendo a disponibilização de equipamento de segurança de rede a essa CONTRATANTE, cuja descrição está con</t>
+          <t>ANULAÇÃO PARCIAL DA NE 73/19, REFERENTE SALDO DE EMPENHO.</t>
         </is>
       </c>
     </row>
@@ -14018,10 +14014,14 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2019NE00264</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr"/>
+          <t>2019NE00268</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C465" t="inlineStr">
         <is>
           <t>01/03/2019</t>
@@ -14037,28 +14037,24 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 73/19, REFERENTE SALDO DE EMPENHO.</t>
+          <t>A CONTRATADA obriga-se a prestar para a CONTRATANTE a Prestação do Serviço de firewall, compreendendo a disponibilização de equipamento de segurança de rede a essa CONTRATANTE, cuja descrição está con</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2018NE00398</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2018NE00337</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>537.03</v>
+        <v>1219.44</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -14067,24 +14063,28 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CONTRATO Nº 009/14 - MÊS DE MARÇO/18 - 05 DIAS.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2018NE00337</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr"/>
+          <t>2018NE00398</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C467" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1219.44</v>
+        <v>537.03</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>PARA ATENDER O CONTRATO Nº 009/14 - MÊS DE MARÇO/18 - 05 DIAS.</t>
         </is>
       </c>
     </row>
@@ -14160,12 +14160,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2018NE00328</t>
+          <t>2018NE00303</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>22/2017</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>5466.68</v>
+        <v>1219.44</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -14183,17 +14183,21 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>PARA ATENDER O MÊS DE FEV/18- PRODAM</t>
+          <t>PARA ATENDER CT.022/17 FEV/18.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2018NE00323</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr"/>
+          <t>2018NE00322</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C471" t="inlineStr">
         <is>
           <t>01/02/2018</t>
@@ -14209,24 +14213,28 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>ANULAÇÃO</t>
+          <t>PARA ATENDER O CT.004/18 - FEV/18.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2018NE00321</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr"/>
+          <t>2018NE00305</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>9/2014</t>
+        </is>
+      </c>
       <c r="C472" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>5466.68</v>
+        <v>3222.16</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -14235,24 +14243,28 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>PARA ATENDER</t>
+          <t>PARA ATENDER CT.009/14 - FEV/18.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2018NE00332</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr"/>
+          <t>2018NE00304</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C473" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>110186.46</v>
+        <v>5466.68</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -14261,28 +14273,24 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>PARA ATENDER O TERMO DE CESSÃO Nº 001/2018 - FMT-HVS E A PRODAM.</t>
+          <t>PARA ATENDER O CT.004/18 - FEV/18.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2018NE00304</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2018NE00332</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>5466.68</v>
+        <v>110186.46</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -14291,28 +14299,24 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CT.004/18 - FEV/18.</t>
+          <t>PARA ATENDER O TERMO DE CESSÃO Nº 001/2018 - FMT-HVS E A PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2018NE00305</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>9/2014</t>
-        </is>
-      </c>
+          <t>2018NE00321</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
       <c r="C475" t="inlineStr">
         <is>
           <t>01/02/2018</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>3222.16</v>
+        <v>5466.68</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -14321,21 +14325,17 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT.009/14 - FEV/18.</t>
+          <t>PARA ATENDER</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2018NE00322</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2018NE00323</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
           <t>01/02/2018</t>
@@ -14351,19 +14351,19 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>PARA ATENDER O CT.004/18 - FEV/18.</t>
+          <t>ANULAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2018NE00303</t>
+          <t>2018NE00328</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>22/2017</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -14372,7 +14372,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1219.44</v>
+        <v>5466.68</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -14381,19 +14381,19 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>PARA ATENDER CT.022/17 FEV/18.</t>
+          <t>PARA ATENDER O MÊS DE FEV/18- PRODAM</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2016NE00176</t>
+          <t>2016NE00177</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>3/2013</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>6444.32</v>
+        <v>10500</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -14418,12 +14418,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2016NE00180</t>
+          <t>2016NE00175</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>2/2013</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1831.44</v>
+        <v>10917</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -14441,19 +14441,19 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE SOFTWARE</t>
+          <t>PRODAM</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2016NE00175</t>
+          <t>2016NE00180</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2/2013</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14462,7 +14462,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>10917</v>
+        <v>1831.44</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -14471,19 +14471,19 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>PRODAM</t>
+          <t>AQUISIÇÃO DE SOFTWARE</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2016NE00177</t>
+          <t>2016NE00176</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>3/2013</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>10500</v>
+        <v>6444.32</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -14686,9 +14686,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Atraso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Corrigido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FMT-HVD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Serviços de Firewall</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>006/2019</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>139429</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03/2023</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>799,08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1073 dias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FMT-HVD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Serviços de Firewall</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>006/2019</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>143872</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>08/2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>669,39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>920 dias</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Suspenso</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TramitarReverter Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DOSSIES_MULTIFORMATO/FMT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FMT/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-04-30</t>
         </is>
       </c>
     </row>
